--- a/Company_Contact.xlsx
+++ b/Company_Contact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00. Projects\6. Mail contact\AutomatedEmailDispatchSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAB71BA-F171-47EC-ACCC-E922F24F0CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57951CE-32E0-473B-8BA1-495542C7DB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="23">
   <si>
     <t>Company_Name</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>C:\Users\USER\Mail Desk\Mridhul_TP_Resume.pdf</t>
-  </si>
-  <si>
-    <t>Sent</t>
   </si>
   <si>
     <t>US Technology International Pvt Ltd</t>
@@ -99,7 +96,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -132,7 +129,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,16 +483,11 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1">
-        <v>46179.642766203702</v>
-      </c>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -509,16 +501,11 @@
       <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1">
-        <v>46179.642800925933</v>
-      </c>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -532,16 +519,11 @@
       <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="1">
-        <v>46179.642847222232</v>
-      </c>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -555,16 +537,11 @@
       <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="1">
-        <v>46179.642881944441</v>
-      </c>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -578,16 +555,11 @@
       <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="1">
-        <v>46179.642916666657</v>
-      </c>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -601,16 +573,11 @@
       <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="1">
-        <v>46179.642962962957</v>
-      </c>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -624,16 +591,11 @@
       <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="1">
-        <v>46179.642997685187</v>
-      </c>
+      <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -647,16 +609,11 @@
       <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="1">
-        <v>46179.64303240741</v>
-      </c>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -670,35 +627,25 @@
       <c r="F10" t="s">
         <v>12</v>
       </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="1">
-        <v>46179.643078703702</v>
-      </c>
+      <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="1">
-        <v>46179.643113425933</v>
-      </c>
+      <c r="H11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
